--- a/traobang.be/traobang.be/Templates/ImportSlide.xlsx
+++ b/traobang.be/traobang.be/Templates/ImportSlide.xlsx
@@ -444,7 +444,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.140625" bestFit="1" customWidth="1"/>
@@ -463,7 +463,7 @@
     <col min="17" max="17" width="12.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -514,12 +514,6 @@
       </c>
       <c r="Q1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="2" t="s">
-        <v>18</v>
       </c>
     </row>
   </sheetData>
